--- a/xls/square_16_quad4_25.xlsx
+++ b/xls/square_16_quad4_25.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>676</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>289</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23">
+        <v>576</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23">
+        <v>1587</v>
+      </c>
+      <c r="I23">
+        <v>-1.0681759481819444</v>
+      </c>
+      <c r="J23">
+        <v>-1.2701091722941877</v>
+      </c>
+      <c r="K23">
+        <v>2.3377092898979877</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24">
+        <v>676</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24">
+        <v>289</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24">
+        <v>625</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24">
+        <v>1728</v>
+      </c>
+      <c r="I24">
+        <v>-1.140474698930441</v>
+      </c>
+      <c r="J24">
+        <v>-1.205979621983574</v>
+      </c>
+      <c r="K24">
+        <v>4.128892752568959</v>
+      </c>
+    </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
         <v>11</v>
@@ -482,13 +552,13 @@
         <v>1875</v>
       </c>
       <c r="I25">
-        <v>-1.399088932706147</v>
+        <v>-0.4659026047720153</v>
       </c>
       <c r="J25">
-        <v>-1.329383840762982</v>
+        <v>-0.407476320006908</v>
       </c>
       <c r="K25">
-        <v>2.628750657972157</v>
+        <v>4.8718906920933644</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -517,13 +587,13 @@
         <v>2028</v>
       </c>
       <c r="I26">
-        <v>-1.4254255359271248</v>
+        <v>-0.17270292869189904</v>
       </c>
       <c r="J26">
-        <v>-1.1519800512317844</v>
+        <v>-0.16794860595291358</v>
       </c>
       <c r="K26">
-        <v>2.9683619822536644</v>
+        <v>4.858116660928715</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -552,13 +622,13 @@
         <v>2187</v>
       </c>
       <c r="I27">
-        <v>-0.5103454503167265</v>
+        <v>-0.0488323821661122</v>
       </c>
       <c r="J27">
-        <v>-0.3304930355883847</v>
+        <v>-0.0412284326037619</v>
       </c>
       <c r="K27">
-        <v>3.1627550269078157</v>
+        <v>4.630588728364858</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -587,13 +657,13 @@
         <v>2352</v>
       </c>
       <c r="I28">
-        <v>-0.003232290420906315</v>
+        <v>-2.4911591853156527e-5</v>
       </c>
       <c r="J28">
-        <v>-0.0033551825374613284</v>
+        <v>-2.7618455891740932e-5</v>
       </c>
       <c r="K28">
-        <v>3.214916752284558</v>
+        <v>3.2190130905874237</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -622,13 +692,13 @@
         <v>2523</v>
       </c>
       <c r="I29">
-        <v>-0.00303557406760523</v>
+        <v>-2.4973999415558442e-5</v>
       </c>
       <c r="J29">
-        <v>-0.003315213204950658</v>
+        <v>-2.7743837254621568e-5</v>
       </c>
       <c r="K29">
-        <v>3.2229863708505717</v>
+        <v>3.1990850487599243</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -657,13 +727,13 @@
         <v>2700</v>
       </c>
       <c r="I30">
-        <v>-0.0011144277515537258</v>
+        <v>-8.29440937097264e-6</v>
       </c>
       <c r="J30">
-        <v>-0.0012118683524027932</v>
+        <v>-9.007401654751651e-6</v>
       </c>
       <c r="K30">
-        <v>3.0328460573622964</v>
+        <v>2.9453153982162186</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -692,13 +762,13 @@
         <v>2883</v>
       </c>
       <c r="I31">
-        <v>-0.002501329099110082</v>
+        <v>-2.214862216135114e-5</v>
       </c>
       <c r="J31">
-        <v>-0.0028591141876151143</v>
+        <v>-2.5357717858771004e-5</v>
       </c>
       <c r="K31">
-        <v>3.2070796975556424</v>
+        <v>3.174028721671562</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -727,13 +797,13 @@
         <v>3072</v>
       </c>
       <c r="I32">
-        <v>-0.0004987759836726075</v>
+        <v>-4.265896550473409e-6</v>
       </c>
       <c r="J32">
-        <v>-0.0005702680650258923</v>
+        <v>-4.884920378367049e-6</v>
       </c>
       <c r="K32">
-        <v>2.883094845827517</v>
+        <v>2.819553630430215</v>
       </c>
     </row>
   </sheetData>
